--- a/artfynd/A 46984-2023 artfynd.xlsx
+++ b/artfynd/A 46984-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,1647 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118889730</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>500191</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6807718</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118889880</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500208</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6807741</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118889931</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90504</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500204</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6807749</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118890019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90430</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500185</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6807839</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118889639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500157</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6807739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118890188</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500266</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6807928</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>118890197</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500300</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6807921</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118890439</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79102</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>500215</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6807986</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118890424</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91779</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>500212</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6807976</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118890415</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>500230</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6807978</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118889995</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>500188</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6807837</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118889653</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>500169</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6807714</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118890202</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>500292</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6807912</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118890235</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>500314</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6807960</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118890396</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>500246</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6807959</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118890267</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78484</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djuptjärnen (Djuptjärnen), Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>500305</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6807963</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46984-2023 artfynd.xlsx
+++ b/artfynd/A 46984-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118889730</v>
+        <v>118890424</v>
       </c>
       <c r="B3" t="n">
-        <v>90504</v>
+        <v>91779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,25 +814,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500191</v>
+        <v>500212</v>
       </c>
       <c r="R3" t="n">
-        <v>6807718</v>
+        <v>6807976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118889880</v>
+        <v>118890188</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,47 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500208</v>
+        <v>500266</v>
       </c>
       <c r="R4" t="n">
-        <v>6807741</v>
+        <v>6807928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118889931</v>
+        <v>118890267</v>
       </c>
       <c r="B5" t="n">
-        <v>90504</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500204</v>
+        <v>500305</v>
       </c>
       <c r="R5" t="n">
-        <v>6807749</v>
+        <v>6807963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118890019</v>
+        <v>118890396</v>
       </c>
       <c r="B6" t="n">
-        <v>90430</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500185</v>
+        <v>500246</v>
       </c>
       <c r="R6" t="n">
-        <v>6807839</v>
+        <v>6807959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118889639</v>
+        <v>118889931</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>90504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500157</v>
+        <v>500204</v>
       </c>
       <c r="R7" t="n">
-        <v>6807739</v>
+        <v>6807749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118890188</v>
+        <v>118889995</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1361,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500266</v>
+        <v>500188</v>
       </c>
       <c r="R8" t="n">
-        <v>6807928</v>
+        <v>6807837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118890197</v>
+        <v>118890235</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1463,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500300</v>
+        <v>500314</v>
       </c>
       <c r="R9" t="n">
-        <v>6807921</v>
+        <v>6807960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118890439</v>
+        <v>118889880</v>
       </c>
       <c r="B10" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,38 +1528,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500215</v>
+        <v>500208</v>
       </c>
       <c r="R10" t="n">
-        <v>6807986</v>
+        <v>6807741</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118890424</v>
+        <v>118889730</v>
       </c>
       <c r="B11" t="n">
-        <v>91779</v>
+        <v>90504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500212</v>
+        <v>500191</v>
       </c>
       <c r="R11" t="n">
-        <v>6807976</v>
+        <v>6807718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118890415</v>
+        <v>118890197</v>
       </c>
       <c r="B12" t="n">
         <v>78484</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500230</v>
+        <v>500300</v>
       </c>
       <c r="R12" t="n">
-        <v>6807978</v>
+        <v>6807921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118889995</v>
+        <v>118890439</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500188</v>
+        <v>500215</v>
       </c>
       <c r="R13" t="n">
-        <v>6807837</v>
+        <v>6807986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118889653</v>
+        <v>118890019</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>90430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500169</v>
+        <v>500185</v>
       </c>
       <c r="R14" t="n">
-        <v>6807714</v>
+        <v>6807839</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,7 +2035,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118890202</v>
+        <v>118889653</v>
       </c>
       <c r="B15" t="n">
         <v>78484</v>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500292</v>
+        <v>500169</v>
       </c>
       <c r="R15" t="n">
-        <v>6807912</v>
+        <v>6807714</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118890235</v>
+        <v>118890415</v>
       </c>
       <c r="B16" t="n">
         <v>78484</v>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500314</v>
+        <v>500230</v>
       </c>
       <c r="R16" t="n">
-        <v>6807960</v>
+        <v>6807978</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118890396</v>
+        <v>118889639</v>
       </c>
       <c r="B17" t="n">
         <v>78484</v>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500246</v>
+        <v>500157</v>
       </c>
       <c r="R17" t="n">
-        <v>6807959</v>
+        <v>6807739</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118890267</v>
+        <v>118890202</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500305</v>
+        <v>500292</v>
       </c>
       <c r="R18" t="n">
-        <v>6807963</v>
+        <v>6807912</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 46984-2023 artfynd.xlsx
+++ b/artfynd/A 46984-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118890424</v>
+        <v>118890197</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,25 +814,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500212</v>
+        <v>500300</v>
       </c>
       <c r="R3" t="n">
-        <v>6807976</v>
+        <v>6807921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118890188</v>
+        <v>118890235</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500266</v>
+        <v>500314</v>
       </c>
       <c r="R4" t="n">
-        <v>6807928</v>
+        <v>6807960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118890267</v>
+        <v>118889931</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500305</v>
+        <v>500204</v>
       </c>
       <c r="R5" t="n">
-        <v>6807963</v>
+        <v>6807749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118890396</v>
+        <v>118889880</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,38 +1120,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500246</v>
+        <v>500208</v>
       </c>
       <c r="R6" t="n">
-        <v>6807959</v>
+        <v>6807741</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118889931</v>
+        <v>118890415</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500204</v>
+        <v>500230</v>
       </c>
       <c r="R7" t="n">
-        <v>6807749</v>
+        <v>6807978</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118889995</v>
+        <v>118889639</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500188</v>
+        <v>500157</v>
       </c>
       <c r="R8" t="n">
-        <v>6807837</v>
+        <v>6807739</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118890235</v>
+        <v>118890424</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>91786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1435,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500314</v>
+        <v>500212</v>
       </c>
       <c r="R9" t="n">
-        <v>6807960</v>
+        <v>6807976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118889880</v>
+        <v>118890439</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>79109</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,47 +1537,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500208</v>
+        <v>500215</v>
       </c>
       <c r="R10" t="n">
-        <v>6807741</v>
+        <v>6807986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118889730</v>
+        <v>118889995</v>
       </c>
       <c r="B11" t="n">
-        <v>90504</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500191</v>
+        <v>500188</v>
       </c>
       <c r="R11" t="n">
-        <v>6807718</v>
+        <v>6807837</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118890197</v>
+        <v>118890396</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500300</v>
+        <v>500246</v>
       </c>
       <c r="R12" t="n">
-        <v>6807921</v>
+        <v>6807959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118890439</v>
+        <v>118890202</v>
       </c>
       <c r="B13" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500215</v>
+        <v>500292</v>
       </c>
       <c r="R13" t="n">
-        <v>6807986</v>
+        <v>6807912</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
         <v>118890019</v>
       </c>
       <c r="B14" t="n">
-        <v>90430</v>
+        <v>90437</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>118889653</v>
       </c>
       <c r="B15" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118890415</v>
+        <v>118889730</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>90511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500230</v>
+        <v>500191</v>
       </c>
       <c r="R16" t="n">
-        <v>6807978</v>
+        <v>6807718</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118889639</v>
+        <v>118890188</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500157</v>
+        <v>500266</v>
       </c>
       <c r="R17" t="n">
-        <v>6807739</v>
+        <v>6807928</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118890202</v>
+        <v>118890267</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500292</v>
+        <v>500305</v>
       </c>
       <c r="R18" t="n">
-        <v>6807912</v>
+        <v>6807963</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 46984-2023 artfynd.xlsx
+++ b/artfynd/A 46984-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118890197</v>
+        <v>118890019</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>90437</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,21 +818,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500300</v>
+        <v>500185</v>
       </c>
       <c r="R3" t="n">
-        <v>6807921</v>
+        <v>6807839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118890235</v>
+        <v>118889931</v>
       </c>
       <c r="B4" t="n">
-        <v>78491</v>
+        <v>90511</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500314</v>
+        <v>500204</v>
       </c>
       <c r="R4" t="n">
-        <v>6807960</v>
+        <v>6807749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118889931</v>
+        <v>118890396</v>
       </c>
       <c r="B5" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500204</v>
+        <v>500246</v>
       </c>
       <c r="R5" t="n">
-        <v>6807749</v>
+        <v>6807959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118889880</v>
+        <v>118889730</v>
       </c>
       <c r="B6" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,47 +1120,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500208</v>
+        <v>500191</v>
       </c>
       <c r="R6" t="n">
-        <v>6807741</v>
+        <v>6807718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118890415</v>
+        <v>118889639</v>
       </c>
       <c r="B7" t="n">
         <v>78491</v>
@@ -1259,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500230</v>
+        <v>500157</v>
       </c>
       <c r="R7" t="n">
-        <v>6807978</v>
+        <v>6807739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118889639</v>
+        <v>118890415</v>
       </c>
       <c r="B8" t="n">
         <v>78491</v>
@@ -1361,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500157</v>
+        <v>500230</v>
       </c>
       <c r="R8" t="n">
-        <v>6807739</v>
+        <v>6807978</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118890424</v>
+        <v>118890267</v>
       </c>
       <c r="B9" t="n">
-        <v>91786</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500212</v>
+        <v>500305</v>
       </c>
       <c r="R9" t="n">
-        <v>6807976</v>
+        <v>6807963</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118890439</v>
+        <v>118890424</v>
       </c>
       <c r="B10" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500215</v>
+        <v>500212</v>
       </c>
       <c r="R10" t="n">
-        <v>6807986</v>
+        <v>6807976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118889995</v>
+        <v>118890235</v>
       </c>
       <c r="B11" t="n">
         <v>78491</v>
@@ -1667,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500188</v>
+        <v>500314</v>
       </c>
       <c r="R11" t="n">
-        <v>6807837</v>
+        <v>6807960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118890396</v>
+        <v>118890439</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500246</v>
+        <v>500215</v>
       </c>
       <c r="R12" t="n">
-        <v>6807959</v>
+        <v>6807986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118890202</v>
+        <v>118890188</v>
       </c>
       <c r="B13" t="n">
         <v>78491</v>
@@ -1871,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500292</v>
+        <v>500266</v>
       </c>
       <c r="R13" t="n">
-        <v>6807912</v>
+        <v>6807928</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118890019</v>
+        <v>118889880</v>
       </c>
       <c r="B14" t="n">
-        <v>90437</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,38 +1936,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djuptjärnen (Djuptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500185</v>
+        <v>500208</v>
       </c>
       <c r="R14" t="n">
-        <v>6807839</v>
+        <v>6807741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118889730</v>
+        <v>118889995</v>
       </c>
       <c r="B16" t="n">
-        <v>90511</v>
+        <v>78491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,21 +2153,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500191</v>
+        <v>500188</v>
       </c>
       <c r="R16" t="n">
-        <v>6807718</v>
+        <v>6807837</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,7 +2239,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118890188</v>
+        <v>118890202</v>
       </c>
       <c r="B17" t="n">
         <v>78491</v>
@@ -2279,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500266</v>
+        <v>500292</v>
       </c>
       <c r="R17" t="n">
-        <v>6807928</v>
+        <v>6807912</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118890267</v>
+        <v>118890197</v>
       </c>
       <c r="B18" t="n">
         <v>78491</v>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500305</v>
+        <v>500300</v>
       </c>
       <c r="R18" t="n">
-        <v>6807963</v>
+        <v>6807921</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
